--- a/AAII_Financials/Quarterly/CITAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CITAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>CITAY</t>
   </si>
@@ -656,61 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +757,23 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +801,23 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +845,23 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +873,13 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +907,23 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +951,23 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +995,23 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +1039,23 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,8 +1064,13 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -964,8 +1098,23 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -993,8 +1142,23 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1170,13 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1035,8 +1204,23 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1248,23 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,8 +1292,23 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1122,8 +1336,23 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1380,23 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,8 +1424,23 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1209,8 +1468,23 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1238,8 +1512,23 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1556,23 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1600,23 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1644,23 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1688,23 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1383,8 +1732,23 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1412,8 +1776,23 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,8 +1820,23 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1470,42 +1864,72 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1941,13 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,269 +1959,409 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2709800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2036600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1469300</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1749400</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1527000</v>
+      </c>
+      <c r="I41" s="3">
         <v>1518700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="J41" s="3">
         <v>1192200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="K41" s="3">
         <v>1540800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="L41" s="3">
         <v>1240100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="M41" s="3">
         <v>1705800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="N41" s="3">
         <v>1837100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="O41" s="3">
         <v>1352700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="P41" s="3">
         <v>1137700</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>300</v>
+      </c>
+      <c r="G42" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I42" s="3">
         <v>4900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="J42" s="3">
         <v>4700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="K42" s="3">
         <v>6200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="L42" s="3">
         <v>5400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="M42" s="3">
         <v>3500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="N42" s="3">
         <v>93300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="O42" s="3">
         <v>84900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="P42" s="3">
         <v>85500</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>926700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>679900</v>
+      </c>
+      <c r="F43" s="3">
+        <v>641500</v>
+      </c>
+      <c r="G43" s="3">
+        <v>926000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>947400</v>
+      </c>
+      <c r="I43" s="3">
         <v>817100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="J43" s="3">
         <v>698800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="K43" s="3">
         <v>888700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="L43" s="3">
         <v>734400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="M43" s="3">
         <v>675300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="N43" s="3">
         <v>660700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="O43" s="3">
         <v>607200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="P43" s="3">
         <v>560300</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>342100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>411200</v>
+      </c>
+      <c r="F44" s="3">
+        <v>408000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>344000</v>
+      </c>
+      <c r="H44" s="3">
+        <v>295100</v>
+      </c>
+      <c r="I44" s="3">
         <v>332600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="J44" s="3">
         <v>310700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="K44" s="3">
         <v>336000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="L44" s="3">
         <v>436200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="M44" s="3">
         <v>463800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="N44" s="3">
         <v>309900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="O44" s="3">
         <v>232800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="P44" s="3">
         <v>435900</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>371200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>578400</v>
+      </c>
+      <c r="F45" s="3">
+        <v>412200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>383000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>345100</v>
+      </c>
+      <c r="I45" s="3">
         <v>261300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="J45" s="3">
         <v>277300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="K45" s="3">
         <v>276100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="L45" s="3">
         <v>395200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="M45" s="3">
         <v>272900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="N45" s="3">
         <v>289200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="O45" s="3">
         <v>47400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="P45" s="3">
         <v>59600</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4349900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3706200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2931400</v>
+      </c>
+      <c r="G46" s="3">
+        <v>3408600</v>
+      </c>
+      <c r="H46" s="3">
+        <v>3120000</v>
+      </c>
+      <c r="I46" s="3">
         <v>2934600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="J46" s="3">
         <v>2483700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="K46" s="3">
         <v>3047700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="L46" s="3">
         <v>2811300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="M46" s="3">
         <v>3121200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="N46" s="3">
         <v>3190200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="O46" s="3">
         <v>2325000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="P46" s="3">
         <v>2279000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4595700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4449500</v>
+      </c>
+      <c r="F47" s="3">
+        <v>4376500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>4177200</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4126200</v>
+      </c>
+      <c r="I47" s="3">
         <v>4061600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="J47" s="3">
         <v>3990600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="K47" s="3">
         <v>4188500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="L47" s="3">
         <v>3971900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="M47" s="3">
         <v>3964800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="N47" s="3">
         <v>3963100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="O47" s="3">
         <v>3808900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="P47" s="3">
         <v>3823300</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8133200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8026300</v>
+      </c>
+      <c r="F48" s="3">
+        <v>7969100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>7287600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>7210600</v>
+      </c>
+      <c r="I48" s="3">
         <v>7137000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="J48" s="3">
         <v>6988500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="K48" s="3">
         <v>6368200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="L48" s="3">
         <v>6338800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="M48" s="3">
         <v>6218400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="N48" s="3">
         <v>6414200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="O48" s="3">
         <v>6265100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="P48" s="3">
         <v>6390500</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>94200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>93700</v>
+      </c>
+      <c r="G49" s="3">
+        <v>88600</v>
+      </c>
+      <c r="H49" s="3">
+        <v>89200</v>
+      </c>
+      <c r="I49" s="3">
         <v>88400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="J49" s="3">
         <v>90000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="K49" s="3">
         <v>88000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="L49" s="3">
         <v>85400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="M49" s="3">
         <v>87100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="N49" s="3">
         <v>90100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="O49" s="3">
         <v>83900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="P49" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2389,23 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2433,67 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>102400</v>
+      </c>
+      <c r="F52" s="3">
+        <v>40200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>33600</v>
+      </c>
+      <c r="H52" s="3">
+        <v>30400</v>
+      </c>
+      <c r="I52" s="3">
         <v>36500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="J52" s="3">
         <v>30900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="K52" s="3">
         <v>33800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="L52" s="3">
         <v>44000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="M52" s="3">
         <v>36600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="N52" s="3">
         <v>43800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="O52" s="3">
         <v>64100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="P52" s="3">
         <v>79300</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2521,67 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20521600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>19691000</v>
+      </c>
+      <c r="F54" s="3">
+        <v>18813800</v>
+      </c>
+      <c r="G54" s="3">
+        <v>18512400</v>
+      </c>
+      <c r="H54" s="3">
+        <v>18187000</v>
+      </c>
+      <c r="I54" s="3">
         <v>17903600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="J54" s="3">
         <v>17312700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="K54" s="3">
         <v>17550100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="L54" s="3">
         <v>17131800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="M54" s="3">
         <v>17353500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="N54" s="3">
         <v>17759500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="O54" s="3">
         <v>16556300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="P54" s="3">
         <v>16735500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2593,13 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2611,277 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>310200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>489900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>304700</v>
+      </c>
+      <c r="G57" s="3">
+        <v>569200</v>
+      </c>
+      <c r="H57" s="3">
+        <v>310400</v>
+      </c>
+      <c r="I57" s="3">
         <v>520800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="J57" s="3">
         <v>301700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="K57" s="3">
         <v>447600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="L57" s="3">
         <v>238300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="M57" s="3">
         <v>361500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="N57" s="3">
         <v>185500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="O57" s="3">
         <v>404900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="P57" s="3">
         <v>68700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6183200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5858400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5835700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>5157600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>5908400</v>
+      </c>
+      <c r="I58" s="3">
         <v>6121000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="J58" s="3">
         <v>4537800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="K58" s="3">
         <v>3434500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="L58" s="3">
         <v>4110100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="M58" s="3">
         <v>4428000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="N58" s="3">
         <v>4657400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="O58" s="3">
         <v>3763800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="P58" s="3">
         <v>3324000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>461200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>178800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>180100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>221700</v>
+      </c>
+      <c r="I59" s="3">
         <v>198800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="J59" s="3">
         <v>192500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="K59" s="3">
         <v>302800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="L59" s="3">
         <v>267600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="M59" s="3">
         <v>277900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="N59" s="3">
         <v>239800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="O59" s="3">
         <v>249200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="P59" s="3">
         <v>558200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6997400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6900700</v>
+      </c>
+      <c r="F60" s="3">
+        <v>6671000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>6035800</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6802500</v>
+      </c>
+      <c r="I60" s="3">
         <v>6960500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="J60" s="3">
         <v>5394000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="K60" s="3">
         <v>4261700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="L60" s="3">
         <v>4931700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="M60" s="3">
         <v>5134000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="N60" s="3">
         <v>5388800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="O60" s="3">
         <v>4482600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="P60" s="3">
         <v>4367600</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8738000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8108600</v>
+      </c>
+      <c r="F61" s="3">
+        <v>7581900</v>
+      </c>
+      <c r="G61" s="3">
+        <v>8012900</v>
+      </c>
+      <c r="H61" s="3">
+        <v>6956800</v>
+      </c>
+      <c r="I61" s="3">
         <v>6584700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="J61" s="3">
         <v>7630800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="K61" s="3">
         <v>8838300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="L61" s="3">
         <v>7956600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="M61" s="3">
         <v>8014300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="N61" s="3">
         <v>8151100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="O61" s="3">
         <v>8005400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="P61" s="3">
         <v>8271700</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>79900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>68700</v>
+      </c>
+      <c r="G62" s="3">
+        <v>75300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>77800</v>
+      </c>
+      <c r="I62" s="3">
         <v>71000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="J62" s="3">
         <v>71900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="K62" s="3">
         <v>73600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="L62" s="3">
         <v>70900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="M62" s="3">
         <v>78600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="N62" s="3">
         <v>73500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="O62" s="3">
         <v>80000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="P62" s="3">
         <v>81600</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2909,23 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2953,23 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2997,67 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15841500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>15114300</v>
+      </c>
+      <c r="F66" s="3">
+        <v>14349100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>14144800</v>
+      </c>
+      <c r="H66" s="3">
+        <v>13860100</v>
+      </c>
+      <c r="I66" s="3">
         <v>13637000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="J66" s="3">
         <v>13119600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="K66" s="3">
         <v>13188000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="L66" s="3">
         <v>12974900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="M66" s="3">
         <v>13240800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="N66" s="3">
         <v>13629800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="O66" s="3">
         <v>12580800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="P66" s="3">
         <v>12735100</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +3069,13 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +3103,23 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +3147,23 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +3191,23 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +3235,67 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2601200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2505200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2411400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2338400</v>
+      </c>
+      <c r="H72" s="3">
+        <v>2305700</v>
+      </c>
+      <c r="I72" s="3">
         <v>2243300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="J72" s="3">
         <v>2164400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="K72" s="3">
         <v>2272600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="L72" s="3">
         <v>2162300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="M72" s="3">
         <v>2174100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="N72" s="3">
         <v>2150800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="O72" s="3">
         <v>2060400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="P72" s="3">
         <v>2058700</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +3323,23 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +3367,23 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +3411,67 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4620700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4512400</v>
+      </c>
+      <c r="F76" s="3">
+        <v>4401900</v>
+      </c>
+      <c r="G76" s="3">
+        <v>4314300</v>
+      </c>
+      <c r="H76" s="3">
+        <v>4274000</v>
+      </c>
+      <c r="I76" s="3">
         <v>4221300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="J76" s="3">
         <v>4150600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="K76" s="3">
         <v>4309600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="L76" s="3">
         <v>4106400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="M76" s="3">
         <v>4112700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="N76" s="3">
         <v>4129800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="O76" s="3">
         <v>3975500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="P76" s="3">
         <v>4000400</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,42 +3499,72 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2618,8 +3592,23 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3620,57 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>207100</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
+        <v>374000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>-195900</v>
+      </c>
+      <c r="H83" s="3">
+        <v>186000</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>351500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="K83" s="3">
         <v>-166500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="L83" s="3">
         <v>164900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>332000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="O83" s="3">
         <v>-154700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="P83" s="3">
         <v>162100</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3698,23 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3742,23 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3786,23 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3830,23 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3874,67 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>71400</v>
+      </c>
+      <c r="F89" s="3">
+        <v>365400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>189200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>109400</v>
+      </c>
+      <c r="I89" s="3">
         <v>69200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="J89" s="3">
         <v>327600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="K89" s="3">
         <v>560800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="L89" s="3">
         <v>3300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="M89" s="3">
         <v>49200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="O89" s="3">
         <v>251400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="P89" s="3">
         <v>445800</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3946,57 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-224300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-304500</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-750000</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-231000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-139200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-240700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="J91" s="3">
         <v>-676300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="K91" s="3">
         <v>-352400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="L91" s="3">
         <v>-229700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="M91" s="3">
         <v>-116100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="N91" s="3">
         <v>-291800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="O91" s="3">
         <v>-173100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="P91" s="3">
         <v>-236300</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +4024,23 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +4068,67 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-170800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-651400</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-48800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>19900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-89200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="J94" s="3">
         <v>-619000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="K94" s="3">
         <v>116500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="L94" s="3">
         <v>-65900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="M94" s="3">
         <v>147800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="N94" s="3">
         <v>-172100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="O94" s="3">
         <v>63000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="P94" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +4140,57 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>128700</v>
+      </c>
+      <c r="F96" s="3">
+        <v>125600</v>
+      </c>
+      <c r="G96" s="3">
+        <v>206200</v>
+      </c>
+      <c r="H96" s="3">
+        <v>130300</v>
+      </c>
+      <c r="I96" s="3">
         <v>130000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="J96" s="3">
         <v>186300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="K96" s="3">
         <v>209800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="L96" s="3">
         <v>141100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="M96" s="3">
         <v>153400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="N96" s="3">
         <v>141700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="O96" s="3">
         <v>291900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="P96" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +4218,23 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +4262,23 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +4306,151 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>454800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>653900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="G100" s="3">
+        <v>73100</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-139100</v>
+      </c>
+      <c r="I100" s="3">
         <v>330000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="J100" s="3">
         <v>-83300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="K100" s="3">
         <v>-360900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="L100" s="3">
         <v>-405800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="M100" s="3">
         <v>-305400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="N100" s="3">
         <v>638000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="O100" s="3">
         <v>-103600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="P100" s="3">
         <v>-630500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>25100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I101" s="3">
         <v>10100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="K101" s="3">
         <v>15900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="L101" s="3">
         <v>29900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="M101" s="3">
         <v>-12800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="N101" s="3">
         <v>15300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="O101" s="3">
         <v>46600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="P101" s="3">
         <v>112900</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>644100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>547200</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-315000</v>
+      </c>
+      <c r="G102" s="3">
+        <v>214400</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="I102" s="3">
         <v>320300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="J102" s="3">
         <v>-349600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="K102" s="3">
         <v>316700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="L102" s="3">
         <v>-455000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="M102" s="3">
         <v>-98300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="N102" s="3">
         <v>463100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="O102" s="3">
         <v>226700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="P102" s="3">
         <v>-53500</v>
       </c>
     </row>
